--- a/AAII_Financials/Quarterly/FMX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FMX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>FMX</t>
   </si>
@@ -656,545 +656,558 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>11525900</v>
+        <v>13220300</v>
       </c>
       <c r="E8" s="3">
+        <v>11520800</v>
+      </c>
+      <c r="F8" s="3">
         <v>12225800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11701900</v>
       </c>
-      <c r="G8" s="3">
-        <v>11176200</v>
-      </c>
       <c r="H8" s="3">
-        <v>9580800</v>
+        <v>11208100</v>
       </c>
       <c r="I8" s="3">
+        <v>9562500</v>
+      </c>
+      <c r="J8" s="3">
         <v>10016600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10048200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10911600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10667000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10817600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10433200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10421800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8837100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7586900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8419200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10031800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8849700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8900000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>22862600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14272500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6786400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6545100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17914300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11323900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5847400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6564200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>18803500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6201700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5618600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5777800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5327900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6282600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5883600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6020000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>16733300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>11212100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5648800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>5836100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>15377700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6861200</v>
+        <v>7920200</v>
       </c>
       <c r="E9" s="3">
+        <v>6858300</v>
+      </c>
+      <c r="F9" s="3">
         <v>7147400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7029100</v>
       </c>
-      <c r="G9" s="3">
-        <v>6633100</v>
-      </c>
       <c r="H9" s="3">
-        <v>5719600</v>
+        <v>6651900</v>
       </c>
       <c r="I9" s="3">
+        <v>5708900</v>
+      </c>
+      <c r="J9" s="3">
         <v>5642300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5995100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6387000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6543000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6242600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6367200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6380000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5397300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3845200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5268400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6312900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5584000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5381400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14174300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8793300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4249300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3932800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>11115000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7050000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3655700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3984500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11798200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3884900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3543700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3509900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3378700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3944000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3757200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3678200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>10691800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>7189300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3636900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3605900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>9738300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4664700</v>
+        <v>5300100</v>
       </c>
       <c r="E10" s="3">
+        <v>4662600</v>
+      </c>
+      <c r="F10" s="3">
         <v>5078400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4672800</v>
       </c>
-      <c r="G10" s="3">
-        <v>4543100</v>
-      </c>
       <c r="H10" s="3">
-        <v>3861200</v>
+        <v>4556200</v>
       </c>
       <c r="I10" s="3">
+        <v>3853600</v>
+      </c>
+      <c r="J10" s="3">
         <v>4374200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4053200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4524600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4124000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4575000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4066000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4041700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3439700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3741700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3150900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3718900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3265700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3518600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8688300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5479200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2537000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2612300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6799200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>4273900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2191700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2579700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7005300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2316700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2074900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2267900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1949200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2338600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2126400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2341800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>6041500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4022800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2011900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2230100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>5639500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1237,8 +1250,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1359,8 +1373,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1481,19 +1498,22 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>-37000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1501,11 +1521,11 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>56200</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1513,11 +1533,11 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-343000</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1525,12 +1545,12 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>54300</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1603,53 +1623,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>429100</v>
+      </c>
+      <c r="E15" s="3">
         <v>402400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>334500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>390400</v>
       </c>
-      <c r="G15" s="3">
-        <v>370800</v>
-      </c>
       <c r="H15" s="3">
+        <v>580100</v>
+      </c>
+      <c r="I15" s="3">
         <v>532700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>230800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>484500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>521200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>592400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>207300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>386600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>472100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>453000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1725,8 +1748,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1766,252 +1792,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10075800</v>
+        <v>12163100</v>
       </c>
       <c r="E17" s="3">
+        <v>10070900</v>
+      </c>
+      <c r="F17" s="3">
         <v>11062500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10742800</v>
       </c>
-      <c r="G17" s="3">
-        <v>10247600</v>
-      </c>
       <c r="H17" s="3">
-        <v>8961500</v>
+        <v>10276800</v>
       </c>
       <c r="I17" s="3">
+        <v>8950200</v>
+      </c>
+      <c r="J17" s="3">
         <v>9189900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9165400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9956600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9917100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10641400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9551500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8973800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8211200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6424500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7668700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9131500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8129700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8010500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20635300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12937500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6242300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5779400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>16976900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10840100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5378900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5928600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>17147300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5621300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5194600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5162300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4892000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5743200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5446600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6797600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>13934800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>10330300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>5095800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5235600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>14216600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1450100</v>
+        <v>1057200</v>
       </c>
       <c r="E18" s="3">
+        <v>1450000</v>
+      </c>
+      <c r="F18" s="3">
         <v>1163400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>959100</v>
       </c>
-      <c r="G18" s="3">
-        <v>928600</v>
-      </c>
       <c r="H18" s="3">
-        <v>619200</v>
+        <v>931300</v>
       </c>
       <c r="I18" s="3">
+        <v>612300</v>
+      </c>
+      <c r="J18" s="3">
         <v>826700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>882900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>955000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>749800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>176100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>881700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1447900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>625800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1162400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>750600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>900300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>719900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>889600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2227300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1335000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>544100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>765700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>937300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>483800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>468400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>635600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1656200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>580300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>424000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>615500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>435900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>539400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>437000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-777600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2798500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>881800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>553000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>600500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1161100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2054,618 +2087,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>30100</v>
+        <v>18800</v>
       </c>
       <c r="E20" s="3">
+        <v>29600</v>
+      </c>
+      <c r="F20" s="3">
         <v>257300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>68700</v>
       </c>
-      <c r="G20" s="3">
-        <v>224700</v>
-      </c>
       <c r="H20" s="3">
-        <v>-79500</v>
+        <v>224000</v>
       </c>
       <c r="I20" s="3">
+        <v>-84600</v>
+      </c>
+      <c r="J20" s="3">
         <v>32600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-196500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-320900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>84800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>158600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-275200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>353100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>175200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-222100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>128500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>84500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-96900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>189800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>626200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>94700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>151200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-319300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>406400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>391700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>448500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>349200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>105300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>24500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>207100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>27900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>386200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-194600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>452000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>360700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>146500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>37400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>186200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>426400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1822400</v>
+        <v>1467500</v>
       </c>
       <c r="E21" s="3">
+        <v>1822800</v>
+      </c>
+      <c r="F21" s="3">
         <v>1240600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1280800</v>
       </c>
-      <c r="G21" s="3">
-        <v>1074700</v>
-      </c>
       <c r="H21" s="3">
-        <v>1231400</v>
+        <v>1287400</v>
       </c>
       <c r="I21" s="3">
+        <v>1229600</v>
+      </c>
+      <c r="J21" s="3">
         <v>1024900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1563900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1797100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1257400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>224800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1543500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1566900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>903600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1382900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1286000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1423000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1048000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1511600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4018800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2175800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1067200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>813000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2368800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1534700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1243900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>960000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2969000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>991600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>751900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1031200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>669700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1145800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>455800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-31000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3778200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1464700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>812000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>996100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>2105900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>303400</v>
+        <v>316400</v>
       </c>
       <c r="E22" s="3">
+        <v>303200</v>
+      </c>
+      <c r="F22" s="3">
         <v>59700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>298200</v>
       </c>
-      <c r="G22" s="3">
-        <v>279700</v>
-      </c>
       <c r="H22" s="3">
-        <v>253400</v>
+        <v>281100</v>
       </c>
       <c r="I22" s="3">
+        <v>252600</v>
+      </c>
+      <c r="J22" s="3">
         <v>62600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>246000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>287900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>281900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>400100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>176000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>134900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>180400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>101800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>193000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>251400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>236400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>245800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>720400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>476100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>209100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>251400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>618100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>455300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>255200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>181800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>525800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>168900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>168200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>121900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>105100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>122700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>138800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>132300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>441400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>300500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>160400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>140600</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>371600</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1181700</v>
+        <v>808300</v>
       </c>
       <c r="E23" s="3">
+        <v>1182200</v>
+      </c>
+      <c r="F23" s="3">
         <v>961600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>696100</v>
       </c>
-      <c r="G23" s="3">
-        <v>532800</v>
-      </c>
       <c r="H23" s="3">
-        <v>549700</v>
+        <v>535000</v>
       </c>
       <c r="I23" s="3">
+        <v>548600</v>
+      </c>
+      <c r="J23" s="3">
         <v>755600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>966700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1194900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>546200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>374400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1129600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1062400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>731200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>838500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>686100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>733400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>386700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>833600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2133200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>953600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>486200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>195100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>725700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>420300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>661700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>449600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1479600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>516700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>280200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>700700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>358800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>802900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>103600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-457900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2717800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>727800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>430000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>646000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1215800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>203200</v>
+        <v>280700</v>
       </c>
       <c r="E24" s="3">
+        <v>202900</v>
+      </c>
+      <c r="F24" s="3">
         <v>389100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>206400</v>
       </c>
-      <c r="G24" s="3">
-        <v>228500</v>
-      </c>
       <c r="H24" s="3">
-        <v>233900</v>
+        <v>230100</v>
       </c>
       <c r="I24" s="3">
+        <v>232900</v>
+      </c>
+      <c r="J24" s="3">
         <v>458200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>303100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>359600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>204000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-179000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>367500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>321600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>226200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>112100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>239300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>279500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>121500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>240400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>575300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>325600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>144900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>158400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>576300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>226000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>148100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>376200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>105100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>93600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>167400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>80300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>231300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>27200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>53900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>474300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>143700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>73700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>177200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>241600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2786,252 +2835,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>978400</v>
+        <v>527700</v>
       </c>
       <c r="E26" s="3">
+        <v>979300</v>
+      </c>
+      <c r="F26" s="3">
         <v>572500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>489700</v>
       </c>
-      <c r="G26" s="3">
-        <v>304300</v>
-      </c>
       <c r="H26" s="3">
-        <v>315800</v>
+        <v>304900</v>
       </c>
       <c r="I26" s="3">
+        <v>315600</v>
+      </c>
+      <c r="J26" s="3">
         <v>297400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>663600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>835300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>342100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>553400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>762100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>740800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>505000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>726300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>446800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>453900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>265100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>593200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1557800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>628000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>341200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>36700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>149500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-80100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>435700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>301500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1103400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>411500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>186600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>533300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>278500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>571600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>76400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-511800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2243400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>584100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>356300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>468800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>974200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>822400</v>
+        <v>316800</v>
       </c>
       <c r="E27" s="3">
+        <v>823200</v>
+      </c>
+      <c r="F27" s="3">
         <v>472800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>131600</v>
       </c>
-      <c r="G27" s="3">
-        <v>143200</v>
-      </c>
       <c r="H27" s="3">
+        <v>143800</v>
+      </c>
+      <c r="I27" s="3">
         <v>284000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>257700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>301200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>689800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>173000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>101900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>559400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>358800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2664700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>521900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>312200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>308200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>153700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>394500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1230200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>417200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>248900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-62500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-33800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-187300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>372300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>237800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>798800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>309400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>108400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>363400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>192800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>465400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>84400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1916300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>322400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>185700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>354300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>768200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3152,8 +3210,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3161,61 +3222,61 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>132600</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-171500</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-8300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>121800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>160400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-191600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>22600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>6700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-276400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-29500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-221000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>2284500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-317200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>261500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>3800</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>85900</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -3226,14 +3287,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3245,37 +3306,40 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>127300</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>18400</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>2700</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>10100</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>182500</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>35400</v>
       </c>
-      <c r="AN29" s="3" t="s">
+      <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3396,8 +3460,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3518,252 +3585,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-30100</v>
+        <v>-18800</v>
       </c>
       <c r="E32" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-257300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-68700</v>
       </c>
-      <c r="G32" s="3">
-        <v>-224700</v>
-      </c>
       <c r="H32" s="3">
-        <v>79500</v>
+        <v>-224000</v>
       </c>
       <c r="I32" s="3">
+        <v>84600</v>
+      </c>
+      <c r="J32" s="3">
         <v>-32600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>196500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>320900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-84800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-158600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>275200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-353100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-175200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>222100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-128500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-84500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>96900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-189800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-626200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-94700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-151200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>319300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-406400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-391700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-448500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-349200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-105300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-24500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-207100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-27900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-386200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>194600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-452000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-360700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-146500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-37400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-186200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-426400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>822400</v>
+        <v>316800</v>
       </c>
       <c r="E33" s="3">
+        <v>823200</v>
+      </c>
+      <c r="F33" s="3">
         <v>472800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>131600</v>
       </c>
-      <c r="G33" s="3">
-        <v>143200</v>
-      </c>
       <c r="H33" s="3">
+        <v>143800</v>
+      </c>
+      <c r="I33" s="3">
         <v>284000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>257700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>301200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>689800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>173000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>101900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>559400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>358800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2664700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>204700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>573800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>312000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>239600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>394500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1230200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>417200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>248900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-62500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-33800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-187300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>372300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>237800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>798800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>309400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>108400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>490600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>211200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>471600</v>
       </c>
-      <c r="AJ33" s="3">
-        <v>0</v>
-      </c>
       <c r="AK33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="3">
         <v>94500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2098800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>357800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>185700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>354300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>768200</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3884,257 +3960,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>822400</v>
+        <v>316800</v>
       </c>
       <c r="E35" s="3">
+        <v>823200</v>
+      </c>
+      <c r="F35" s="3">
         <v>472800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>131600</v>
       </c>
-      <c r="G35" s="3">
-        <v>143200</v>
-      </c>
       <c r="H35" s="3">
+        <v>143800</v>
+      </c>
+      <c r="I35" s="3">
         <v>284000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>257700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>301200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>689800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>173000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>101900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>559400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>358800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2664700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>204700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>573800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>312000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>239600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>394500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1230200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>417200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>248900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-62500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-33800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-187300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>372300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>237800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>798800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>309400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>108400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>490600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>211200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>471600</v>
       </c>
-      <c r="AJ35" s="3">
-        <v>0</v>
-      </c>
       <c r="AK35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="3">
         <v>94500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2098800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>357800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>185700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>354300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>768200</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4177,8 +4262,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4221,142 +4307,146 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6006900</v>
+      </c>
+      <c r="E41" s="3">
         <v>5930100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5997800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6740400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6884300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5349800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6710700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7954500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6647100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8299400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9766500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9213600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8981000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5539000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4348800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5396000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6342300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5583100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5720700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6477600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5875300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6177500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5404900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6642300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6710500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6386500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3253200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4914100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3408800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3620700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2829300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2438000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2888300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4348400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5014000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5220300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2640300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2123900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2317100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3068800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>742200</v>
       </c>
       <c r="E42" s="3">
+        <v>491300</v>
+      </c>
+      <c r="F42" s="3">
         <v>1113200</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -4364,11 +4454,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>2073800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -4376,11 +4466,11 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>1581000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -4388,939 +4478,963 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>595200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>567700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>624700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1537600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1579500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>662300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>613300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>67600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>67400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>184600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>187500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1279800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>670500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>810500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1079200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>934400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1450200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1074600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1364500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>735500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>150800</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>120300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>109400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>131800</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>150000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>68800</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4437400</v>
+      </c>
+      <c r="E43" s="3">
         <v>4260100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4383200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4052000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3741400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3585500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3337100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3176900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3281500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3541200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4479300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3634700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3811600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3285100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3382000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3100600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3267200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3092700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3053300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2640500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2424400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2359800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2277400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2201200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2042000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2120000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2401300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2164100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2092400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1956400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2036100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1821000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2182200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2125000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2255000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1847100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1678400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1684600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1882300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1572300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3866000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3752900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3857800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3461100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3531900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3255900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3237600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3225800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3162300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3293200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3443900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3203300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3414900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3398600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3243100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2949100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3285200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3161400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2989100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2690000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2419500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2369500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2211400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1998000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1996700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1959100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2035600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1815000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1810900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1654800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1627300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1464700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1855600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1840100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1801900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1590400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1600200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1712300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1695600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1497600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>996500</v>
+        <v>520200</v>
       </c>
       <c r="E45" s="3">
+        <v>505200</v>
+      </c>
+      <c r="F45" s="3">
         <v>353700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1906800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2984000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4128600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1051700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2988200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6138000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5832200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1778500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5680800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2110000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6297500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>233400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>308700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>303900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>397500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>207400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>192300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>195200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>193000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>146600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>209600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>239200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>235700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>202800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>186500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>187400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>200100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>155900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1441200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>213000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>238900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>149400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>282600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>275200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>291400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>218200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>222000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15572600</v>
+      </c>
+      <c r="E46" s="3">
         <v>14939600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15725900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16160400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17141600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16319900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16427700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17345400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19228900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20966000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21067100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21732400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18317400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18520300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11802500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12322100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13823300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13772300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13550100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12662800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>11527700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>11167400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10107700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>11235700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>11175900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>11981100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8563400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9890100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8578700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8366400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8098900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8239500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8503500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>9287900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>9371000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>9060700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6303600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>5943900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>6263200</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>6429500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2413200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2399200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1531100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1933500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1893600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2333800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1775700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2428100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1952000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1909300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2090900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>914100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>977400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1947300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>5770700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6987900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7730700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8436700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8825600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8369500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7174400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7507800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6647000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7112300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7172700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7540500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5406600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5447100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5615600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5646300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5440900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5754400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7101200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5807800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5676600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5049500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>6170800</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>6245900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>7734700</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>7394700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16902900</v>
+      </c>
+      <c r="E48" s="3">
         <v>16407500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16064600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15546200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14930000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13833000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13220000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13287200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13235200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13815400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13573400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12834500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12674900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11930400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11360400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9723200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10579000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10627300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10109900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9480900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9062300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9047100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8429600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8323200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8087600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8260500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8296300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8146800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7790300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7620900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4952300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4640900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6244000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6014700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>6036300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>5909300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>5632200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>6023200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>5428000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>4860600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8360100</v>
+      </c>
+      <c r="E49" s="3">
         <v>8177800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8130200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7949000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7768600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7308600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7071500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7509900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7789300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8519000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8516800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8793800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10937700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10347000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9943000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8837900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9860700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9895800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9287400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8669900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8442000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8365600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7809300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7918400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7868700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7092800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7272400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7237000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7164400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6987700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6639800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6352400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8114000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7946700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7969700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>7822000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>7538600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>7939600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>8138600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>6650900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5441,8 +5555,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5563,130 +5680,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>712600</v>
+      </c>
+      <c r="E52" s="3">
         <v>715100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1033000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>746400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>708800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>655500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1079300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1052800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1040200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1095600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>786500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1045200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1086400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>647100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2757600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1760600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1944300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1853800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1540400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1607300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1608600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1471700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1399600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1428400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1326600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1550100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2096100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1396400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1286200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1228800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1151100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1154300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1384800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1558000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1385700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1469000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1448900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1441100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1408100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>834700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5807,130 +5930,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>45931900</v>
+      </c>
+      <c r="E54" s="3">
         <v>44450400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>44207500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>44049300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>44067900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>41875200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40865800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43400500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44910300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>48129900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>47667100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>46983600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>45546600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>44937300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>41634200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>39631700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>43938000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>44585800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>43313300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>40790400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>37815000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>37559500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34393100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>36018000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35631400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>36425000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>31634800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>32117500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30435300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29850000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>26283000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>26141400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>31347500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>30615100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>30439300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>29310600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>27094100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>27593600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>28972600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>26170300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5973,8 +6102,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6017,740 +6147,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5213300</v>
+      </c>
+      <c r="E57" s="3">
         <v>4921100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5215100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4823000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4716400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4388500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4728900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4351100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4319000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4547800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4870000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4586800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4388900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3988000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5745800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3725100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4140800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3967900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3888100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3287200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3085800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2837100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2662600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2433400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2430900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2610000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2837200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2610000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2583900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2264200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2375800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2140400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2584500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2607900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2514900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2224100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2201800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2162300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2520300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2085100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1738800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1254400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1992000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1761700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1845900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1693200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>984700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1156300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1025800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1044600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1223700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>992100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1010200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1686600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1586300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1360100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1471800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>760900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>701600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>678500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>710600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>800700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>782100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1317800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2201500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1945000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1173500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1400500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1195000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1187100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>624500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>556100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>773200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>695200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>703700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>349100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>348400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>376500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>390500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>321600</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5878100</v>
+      </c>
+      <c r="E59" s="3">
         <v>5938000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1963100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4643200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5561100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3222100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1821100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4469400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5289500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6341500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2402800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4728900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4120300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4205800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1889000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3865000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4204800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3833900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3440000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3530500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3124600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3306700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2502100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2923100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2938100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2911500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2764200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2496200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2356000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2565400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1626500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2349300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2343600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3077300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2213200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2248200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1946300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2446700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1671100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1845300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13705200</v>
+      </c>
+      <c r="E60" s="3">
         <v>12923000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11665400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12047000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12799300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9951300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9738700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10693200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11190400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12475900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10788000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11080900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10198500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10546300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9221200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8950200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9817400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8562800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8029700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7496200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6921100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6944500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5946700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6674300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7570500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7466600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6774800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6506600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6135000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6016700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4626800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5045900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5701200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6380300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5431700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4821300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4496400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4985600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4581900</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4252000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12740700</v>
+      </c>
+      <c r="E61" s="3">
         <v>13043600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12314200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12278000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12231800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11107500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11315300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11809500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11995000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12582900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12552400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12577700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12545300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12225300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13270900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11520100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13240100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14185500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14153600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13442500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12719400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>12841100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>11620900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>12200400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11158100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10698300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7396000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7501400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7175100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>7162700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5323600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5603300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>6905500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6021000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6105500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>6173300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>6577600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>6282100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>7034400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>6295900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1148000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1032100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>878300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>847600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>820200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>706600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>673500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>790700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>906000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1169400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1100500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>951800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1025500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>784500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1536000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1517100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1665300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1798700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1466300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1483100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1509300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1430500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1398500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1367600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1422400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1616400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1300200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1188100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1174400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1112900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1031800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>958000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1332900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1460100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1477000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2117200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1803100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2079400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2160700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1399500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6871,8 +7020,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6993,8 +7145,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7115,130 +7270,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28709300</v>
+      </c>
+      <c r="E66" s="3">
         <v>28125300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25913400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26197600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26831400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22707000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22575000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24135600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24915600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27166700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25286300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25397100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>24452500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>24919100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27947300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>25837200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28949400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28785700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>27908400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26369700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>24869400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>24745300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22453600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23835300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23686000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23260200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19131100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19081300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>18221500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>17923700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14561300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>15249900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>18359600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>18123900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>17494300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>17372700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>16898000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>17468200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>17720500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>15539000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7281,8 +7442,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7403,8 +7565,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7525,8 +7690,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7647,8 +7815,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7769,130 +7940,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14796600</v>
+      </c>
+      <c r="E72" s="3">
         <v>14033400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15487500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14710500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14180300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15275000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>14704300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15372400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16155200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17053500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18020500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17395000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17097900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15910200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13092100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13042800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13933300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14375900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14266600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>276172800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12039600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>11812400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>10828200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10879300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10250800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11130900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>11445500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11406000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10500400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>10225500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9995700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9309500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>10892000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>10378700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>10576000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>10388300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8797900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8529300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>9104500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>8703200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8013,8 +8190,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8135,8 +8315,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8257,130 +8440,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12422100</v>
+      </c>
+      <c r="E76" s="3">
         <v>11824500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>13607700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13369800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12964200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>14821000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14277300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15062500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15883700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16724400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17973600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17303000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16971600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16179100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13686900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13794500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14988600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15800100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15404900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14420700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12945600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12814200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11939500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12182700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11945400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13164800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12503700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13036200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12213700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>11926400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11721600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>10891500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12987900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12491200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12945000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>11937800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>10196100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>10125400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>11252100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>10631400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8501,257 +8690,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>822400</v>
+        <v>316800</v>
       </c>
       <c r="E81" s="3">
+        <v>823200</v>
+      </c>
+      <c r="F81" s="3">
         <v>472800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>131600</v>
       </c>
-      <c r="G81" s="3">
-        <v>143200</v>
-      </c>
       <c r="H81" s="3">
+        <v>143800</v>
+      </c>
+      <c r="I81" s="3">
         <v>284000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>257700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>301200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>689800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>173000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>101900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>559400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>358800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2664700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>204700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>573800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>312000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>239600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>394500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1230200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>417200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>248900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-62500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-33800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-187300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>372300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>237800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>798800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>309400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>108400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>490600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>211200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>471600</v>
       </c>
-      <c r="AJ81" s="3">
-        <v>0</v>
-      </c>
       <c r="AK81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="3">
         <v>94500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2098800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>357800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>185700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>354300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>768200</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8794,130 +8992,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>580100</v>
+      </c>
+      <c r="E83" s="3">
         <v>532700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>305900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>484500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>521200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>592400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>526300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>386600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>472100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>453000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>353900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>324300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>363000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>356100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>442700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>406900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>438200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>425000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>432200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1165300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>746100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>371900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>366600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1025100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>659200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>327000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>328600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>963600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>306000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>303500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>208600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>167100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>244300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>235500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>221800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>691900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>436400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>221600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>209500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>518500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9038,8 +9240,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9160,8 +9365,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9282,8 +9490,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9404,8 +9615,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9526,130 +9740,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1898400</v>
+      </c>
+      <c r="E89" s="3">
         <v>1248900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1172100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1414100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>907600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>338800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1326900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>560300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1191400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>730200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>562900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1314200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>841900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>157500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1209300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>869100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1343600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>612800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1120200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3017200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1918700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>708200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>980600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1643800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>889100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>582800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>624700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2463200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>919700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>733300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>739800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>398100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>536900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>712800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>525200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1592200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>927300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>255900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>917700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1744300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9692,130 +9912,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-456400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-384500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-609600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-564400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-435600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-438400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-690800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-637700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-626600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-323000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-764500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-592200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-364000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-295800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-12987000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9284000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5224000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6618000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5139000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6666000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-432800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-175300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>23000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-86600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-40700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-37000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-55600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>28200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-35300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-14600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-30200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-70800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-44600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-53100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-23400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-479200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-748700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9936,8 +10160,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10058,130 +10285,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-676400</v>
+      </c>
+      <c r="E94" s="3">
         <v>406200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-333700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>30000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1395500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1121400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1428100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1460600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-641000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1222400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1814900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-978000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4501200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2297900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2112500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-470700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>720500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-572600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1405900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1225400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-827600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-123600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-792600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-769900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-491700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-150300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1298800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>604800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-496800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>424600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>264000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2310100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1054300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-868900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>2452200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-110500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-102600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1316800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-735300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10224,104 +10457,105 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>702300</v>
+      </c>
+      <c r="E96" s="3">
         <v>652000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>883900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>755000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>748300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>296100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>435800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>412500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>433700</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>166900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>8000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>541500</v>
       </c>
-      <c r="P96" s="3" t="s">
+      <c r="Q96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-453200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-4100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-523100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-391000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-380900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-363200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-397400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-393000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-128900</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-338000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-342300</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-294800</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
@@ -10329,25 +10563,28 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-319900</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-324000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-316400</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
       <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-321400</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-318200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10468,8 +10705,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10590,8 +10830,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10712,370 +10955,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1225900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1801200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1596400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1621100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-949400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-764300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-909100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-820100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1737800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1044000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2138500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-380900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1486700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1345500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>45400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-747200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-970000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-377900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-726700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1390500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-989400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-308400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1037800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1987900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2576900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2030800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-781300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1139400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-531700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-448300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-871900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-122300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>65400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-128200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-634700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-479300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-164300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-181700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-320200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>389100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-267600</v>
+      </c>
+      <c r="E101" s="3">
         <v>55100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>245500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>552900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>305900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-128300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>36900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>415200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-703600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-196000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-91300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>84700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-277300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>73000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-61000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>90800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-334800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>87100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-92900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>34800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-517500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>541700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>599000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>786100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-148600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-128800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-66400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-90100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>181100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-227000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>286100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-368100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>406900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-236500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-269200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-104600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-32200</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>109700</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-111300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-59600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-869500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-337500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1086000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1491800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-764800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1753700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-881500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1664400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>276200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>370500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3152900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>913900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-918800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-258000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>759200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-250600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1013700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>397900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>310900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1367300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3403500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3573300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3249400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1602200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1798100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-175200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>619500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>359400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>13000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1460100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-848800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-208500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>2965500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>383400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-133000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-751600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1507800</v>
       </c>
     </row>
